--- a/Selenium/Selenimproject/Utilities/Readdata.xlsx
+++ b/Selenium/Selenimproject/Utilities/Readdata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\demo3\Utilities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Selenium\Selenium\Selenimproject\Utilities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA53A78-8575-4604-BD14-0912BB077018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B0336B-AC7C-4A6F-9E1B-B8ED9EF11D88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1410" yWindow="1650" windowWidth="18240" windowHeight="9030" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Readdata" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>test</t>
   </si>
@@ -29,6 +29,12 @@
   </si>
   <si>
     <t>pas</t>
+  </si>
+  <si>
+    <t>rgfg</t>
+  </si>
+  <si>
+    <t>vvv</t>
   </si>
 </sst>
 </file>
@@ -512,9 +518,8 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -870,14 +875,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
@@ -892,6 +897,14 @@
         <v>123</v>
       </c>
     </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
